--- a/P(Path)/RP(Rhine-Path)/RheinWegDE/Wiesbaden.xlsx
+++ b/P(Path)/RP(Rhine-Path)/RheinWegDE/Wiesbaden.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hotel" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="restaurant" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kino" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="taxi" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -43072,4 +43073,3552 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="7" min="1" max="1"/>
+    <col width="34.66" customWidth="1" style="7" min="2" max="2"/>
+    <col width="22" customWidth="1" style="7" min="3" max="3"/>
+    <col width="36" customWidth="1" style="7" min="4" max="4"/>
+    <col width="12" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10" customWidth="1" style="7" min="6" max="6"/>
+    <col width="28" customWidth="1" style="7" min="7" max="7"/>
+    <col width="28" customWidth="1" style="7" min="8" max="8"/>
+    <col width="18" customWidth="1" style="7" min="9" max="9"/>
+    <col width="16" customWidth="1" style="7" min="10" max="10"/>
+    <col width="16" customWidth="1" style="7" min="11" max="11"/>
+    <col width="16" customWidth="1" style="7" min="12" max="12"/>
+    <col width="32" customWidth="1" style="7" min="13" max="13"/>
+    <col width="32" customWidth="1" style="7" min="14" max="14"/>
+    <col width="40" customWidth="1" style="7" min="15" max="15"/>
+    <col width="42" customWidth="1" style="7" min="16" max="16"/>
+    <col width="26" customWidth="1" style="7" min="17" max="17"/>
+    <col width="9" customWidth="1" style="7" min="18" max="18"/>
+    <col width="10" customWidth="1" style="7" min="19" max="19"/>
+    <col width="11" customWidth="1" style="7" min="20" max="20"/>
+    <col width="16" customWidth="1" style="7" min="21" max="21"/>
+    <col width="45" customWidth="1" style="7" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="7">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>🚕  Taxi – Wiesbaden  ·  46 Companies  ·  Source: GelbeSeiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="7">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Business Description</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>ZIP Code</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>Street</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>Contact Person</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 1</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 2</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 3</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Email 2</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="P2" s="11" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="Q2" s="11" t="inlineStr">
+        <is>
+          <t>Opening Hours</t>
+        </is>
+      </c>
+      <c r="R2" s="11" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="inlineStr">
+        <is>
+          <t># Reviews</t>
+        </is>
+      </c>
+      <c r="T2" s="11" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="U2" s="11" t="inlineStr">
+        <is>
+          <t>Badge / Partner</t>
+        </is>
+      </c>
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>GelbeSeiten URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbadener Taxizentrale</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>ADAC-Service, Wiesbadener Taxi - Zentrale, Flughafentransfer, Krankenfahrten, Kurierdienst, Lotsendienst, Personentransport, Sachtransport, Stadtrundfahrt, Weckdienst, Großraumtaxe</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Kreuzberger Ring 50</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>0611 33 33 33</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>wtz@taxiwiesbaden.de</t>
+        </is>
+      </c>
+      <c r="N3" s="13" t="n"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>http://www.taxiwiesbaden.de/</t>
+        </is>
+      </c>
+      <c r="P3" s="13" t="n"/>
+      <c r="Q3" s="13" t="n"/>
+      <c r="R3" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="13" t="inlineStr">
+        <is>
+          <t>4,6 km</t>
+        </is>
+      </c>
+      <c r="U3" s="13" t="n"/>
+      <c r="V3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/4eadfe33-2b41-4838-9f7a-dd8af8142838</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Taxi Saim Großraumtaxi</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Airportshuttle, Chauffeurservice, Dialysefahrten, Flughafentransfer, Großraumtaxi, Kleinbus bis 7 Personen, Krankenfahrten, Limousine, Messetransfer, Shuttleservice</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>65931</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>0177 2 10 02 15</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>info@grossraumtaxi-frankfurt.de</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n"/>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>http://www.grossraumtaxi-frankfurt.de/</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="n"/>
+      <c r="Q4" s="15" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="15" t="n"/>
+      <c r="U4" s="15" t="n"/>
+      <c r="V4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/37a5e0fc-8306-4299-bbfe-50ec43e3e7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Hamid</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Otto-Wels-Str.</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>0178 5 31 83 74</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>zahirhamid@arcor.de</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>Mo 06:00-20:00; Di 06:00-20:00; Mi 06:00-20:00; Do 06:00-20:00; Fr 06:00-20:00; Sa 06:00-20:00; So 06:00-20:00</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="13" t="inlineStr">
+        <is>
+          <t>2,7 km</t>
+        </is>
+      </c>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/9512ea63-fa78-495e-a7bf-c7094297178e</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>CleverTaxi Wiesbaden</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>65187</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Schiersteiner Str. 6</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>0611 13 71 37 17</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>info@clevertaxi-wi.de</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.clevertaxi-wi.de/</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>1,3 km</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ae550572-c118-439d-b786-7ff053a19648</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Krieger Gero Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen, Kurierdienste, Personenbeförderung</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Steinmetzstr. 2</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>0160 6 86 77 55</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>taxi-gk@gmx.de</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="13" t="n"/>
+      <c r="R7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t>1,7 km</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/87a96793-1acc-4188-be27-9b8bf4e39c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Taxi Ahmed</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Kurierdienst, 1 bis 8 Personen Taxi</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Eschbornstr. 13</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>0611 94 69 26 75</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>taxi4wiesbaden@gmail.com</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="15" t="inlineStr">
+        <is>
+          <t>2 km</t>
+        </is>
+      </c>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/c55f7380-0636-4dc4-bfe5-874d8870ad2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Ahmed</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Dekan-Lindenbein-Str. 13</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>0176 41 19 78 63</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>qasim_ahm@yahoo.com</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t>9,4 km</t>
+        </is>
+      </c>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5b735040-227a-4562-86d1-d999a45e4c2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>ALS - Automotive Limousines &amp; Shuttle</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>65193</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Rößlerstraße 3</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>0611 76 36 98 25</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>kontakt@als-limousines.de</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.als-limousines.de/</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R10" s="14" t="n"/>
+      <c r="S10" s="14" t="n"/>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>350 m</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/b4ef4e7c-cae1-40d1-8fcd-6bfaf12488d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Wiesbaden 24 Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Krankenfahrten, Taxi, Taxi Flughafen, Dialysefahrten, Besorgungsfahrten, Flughafentransfer</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>65191</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Meißener Str. 34</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>0173 4 26 36 88</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>behzadrana@hotmail.de</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>http://taxi-wiesbaden-24.de/</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="n"/>
+      <c r="R11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>3,1 km</t>
+        </is>
+      </c>
+      <c r="U11" s="13" t="n"/>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/8952ab13-637a-4900-a1de-cac40d115535</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Fazli Wali Taxiuntnternehmen</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Taxiservice, Flughafentransfer, Airporttransfer, Shuttleservice, Taxi</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Hermann-Brill-Str. 12</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>0611 13 72 63 66</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>wali007@rocketmail.com</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>3,6 km</t>
+        </is>
+      </c>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5d4b67ab-eed1-4fb8-ba2b-0c241f77c9ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Blanco</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>65199</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Hans-Böckler-Str. 12</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>0151 41 48 07 79</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>taxiblanco@outlook.de</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>http://www.taxiblanco-wi.de/</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R13" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t>4,3 km</t>
+        </is>
+      </c>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/75864937-767d-4c08-adad-c041b954a0e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Shakeri Farid Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Botenfahrten, Corona, Einkaufen, Flughafen, Freundlich, Großraum, Großraum Taxi, Schnell, Taxi, Wiesbaden, Zuverlässig</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>65193</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Platter Str. 70</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>0176 22 35 51 20</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>farid.shakeri2@gmail.com</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>1,1 km</t>
+        </is>
+      </c>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/95b094a5-52cc-4cd2-a145-41ad408332ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Dillemuth</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>65195</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Emser Str. 50</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>0611 9 88 69 62</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
+          <t>1,2 km</t>
+        </is>
+      </c>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/6184d872-aaa6-4751-81f0-d49829fe989a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Aster Tanja Taxi</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Flughafentransfer, Frauentaxi, Taxi, Taxiunternehmen, Taxifahrt, Taxen</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>65189</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Martinstr. 17</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>0174 7 92 00 47</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>tanjaaster66@googlemail.com</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="inlineStr">
+        <is>
+          <t>Mo 12:00-20:00; Di 12:00-20:00; Mi 12:00-20:00; Do 12:00-20:00; Fr 12:00-20:00; Sa 12:00-20:00; So 12:00-20:00</t>
+        </is>
+      </c>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="15" t="inlineStr">
+        <is>
+          <t>1,3 km</t>
+        </is>
+      </c>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/83335264-1570-4f2f-b2a4-934ce0139f4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Athanatos Taxi Wiesbaden</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Steinmetzstr. 2</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>0177 2 58 25 88</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>taxi@wiesbaden-airport-service.de</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wiesbaden_airport_service</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R17" s="12" t="n"/>
+      <c r="S17" s="12" t="n"/>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>1,7 km</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ce1b1da7-6831-4d9a-8010-695d2e8a85c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Taxi Herzog</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Flughafenfahrten, Frauentaxi</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>65191</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Kemmelweg 10</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>0171 7 76 11 22</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>2 km</t>
+        </is>
+      </c>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/306e25a2-c678-4e05-b361-0ce7fad46001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Amir Mansouri Gilani Daryoush</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>65187</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Konrad-Adenauer-Ring 38</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>0171 4 42 13 66</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t>2 km</t>
+        </is>
+      </c>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/a3c383ea-e8f1-4558-b74f-ba8395ed0c02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Wichelmann Taxi</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Flughafen-Transfer, Personentransporte, Taxi</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Anton-Berges-Str. 3</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>0611 2 27 53</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>taxiwichelmann@t-online.de</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>http://www.taxi-wichelmann.de/</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>5,4 km</t>
+        </is>
+      </c>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ad8e9d8d-9076-4dac-8cd8-3fdfc4a38216</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Dieter Edgar Taxi</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>65191</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Ländchenweg 30</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>0611 50 23 55</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="13" t="inlineStr">
+        <is>
+          <t>3,2 km</t>
+        </is>
+      </c>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/7532307a-9606-4d97-a159-a6deb3220508</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Y-Taxiservice</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Taxi</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>65199</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Föhrer Str. 76</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>0800 3 00 00 09</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>said.mehran@hotmail.de</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="inlineStr">
+        <is>
+          <t>https://y-taxiservice.business.site/</t>
+        </is>
+      </c>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="inlineStr">
+        <is>
+          <t>Mo 00:30-24:00; Di 00:30-24:00; Mi 00:30-24:00; Do 00:30-24:00; Fr 00:30-24:00; Sa 00:30-24:00; So 00:30-24:00; Fe 00:30-24:00</t>
+        </is>
+      </c>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
+      <c r="T22" s="15" t="inlineStr">
+        <is>
+          <t>3,4 km</t>
+        </is>
+      </c>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/0ece2e71-4d41-48fc-bff0-2901d945aebd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Pervaiz</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>65187</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Klagenfurter Ring 67</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>0178 5 10 86 11</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>Taxipervaiz@gmail.com</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="n"/>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>http://taxi-wiesbaden.eu/</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R23" s="12" t="n"/>
+      <c r="S23" s="12" t="n"/>
+      <c r="T23" s="13" t="inlineStr">
+        <is>
+          <t>3,5 km</t>
+        </is>
+      </c>
+      <c r="U23" s="13" t="n"/>
+      <c r="V23" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/7079cebd-529d-4ace-8107-15dc8f8be7e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Taxi Raoufi</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>65203</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Am Hohen Stein 20</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>0176 63 29 76 75</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t>assad.raoufi@gmail.com</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="inlineStr">
+        <is>
+          <t>http://www.taxiwiesbaden-flughafen.de/</t>
+        </is>
+      </c>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="inlineStr">
+        <is>
+          <t>Mo 00:00-23:30; Di 00:00-23:30; Mi 00:00-23:30; Do 00:00-23:30; Fr 00:00-23:30; Sa 00:00-23:30; So 00:00-23:30; Fe 00:00-23:30</t>
+        </is>
+      </c>
+      <c r="R24" s="14" t="n"/>
+      <c r="S24" s="14" t="n"/>
+      <c r="T24" s="15" t="inlineStr">
+        <is>
+          <t>3,7 km</t>
+        </is>
+      </c>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/7427f219-ca58-4b5f-9162-08f30a10f2fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Taxi König</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>Untergasse 8</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>0177 2 76 60 50</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="inlineStr">
+        <is>
+          <t>ghafaramir8@gmail.com</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>http://taxikoenigwiesbaden.de/</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="n"/>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="13" t="inlineStr">
+        <is>
+          <t>6,8 km</t>
+        </is>
+      </c>
+      <c r="U25" s="13" t="n"/>
+      <c r="V25" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/f11253d6-02d6-42af-a5f1-fb5f53287826</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Markus Michel Taxibetrieb</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Köpenicker Str. 4</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>0151 42 50 99 99</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="15" t="n"/>
+      <c r="M26" s="15" t="n"/>
+      <c r="N26" s="15" t="n"/>
+      <c r="O26" s="15" t="inlineStr">
+        <is>
+          <t>http://www.wiesbaden-airportservice.de/</t>
+        </is>
+      </c>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="14" t="n"/>
+      <c r="S26" s="14" t="n"/>
+      <c r="T26" s="15" t="inlineStr">
+        <is>
+          <t>4,2 km</t>
+        </is>
+      </c>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ac6e7471-0cae-4add-88a8-1965e90bc673</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Munish</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>55252</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbadener Straße 71</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>06134 24 00 05</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>chawla@taxi-munish.de</t>
+        </is>
+      </c>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.taxi-munish.de/</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="n"/>
+      <c r="Q27" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" s="13" t="inlineStr">
+        <is>
+          <t>7,6 km</t>
+        </is>
+      </c>
+      <c r="U27" s="13" t="n"/>
+      <c r="V27" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/579b3a1c-4556-45a5-be63-77bfd28695e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Muneeb Mubashir Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Flughafentransfer, Personenbeförderung, Krankentransporte</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>55252</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Mainz-Kastel</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Boelckestr. 26A</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="n"/>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>06134 5 00 06 09</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>booking@taximuneeb.de</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="n"/>
+      <c r="O28" s="15" t="inlineStr">
+        <is>
+          <t>http://www.taximuneeb.de/</t>
+        </is>
+      </c>
+      <c r="P28" s="15" t="n"/>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T28" s="15" t="inlineStr">
+        <is>
+          <t>8,2 km</t>
+        </is>
+      </c>
+      <c r="U28" s="15" t="n"/>
+      <c r="V28" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/cc9898ad-42a1-4b71-95bf-48c1889ceac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Jamali Taxibetrieb</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Mietwagen</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Freiherr-vom-Stein-Str. 4A</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>06122 7 07 07 90</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>taxi.jamali@googlemail.com</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.taxi-wiesbaden.com/</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="n"/>
+      <c r="R29" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S29" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" s="13" t="inlineStr">
+        <is>
+          <t>8,1 km</t>
+        </is>
+      </c>
+      <c r="U29" s="13" t="n"/>
+      <c r="V29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/7b56b6b3-c45c-4540-b297-e6ae2c51634f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Taxi-Team Wiesbaden Markus Meyer e.K. Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Kurierfahrten, Flughafentransfer, Frauentaxi</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Alte Schmelze 21</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="inlineStr">
+        <is>
+          <t>0611 40 40 31</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
+      <c r="M30" s="15" t="n"/>
+      <c r="N30" s="15" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="14" t="n"/>
+      <c r="S30" s="14" t="n"/>
+      <c r="T30" s="15" t="inlineStr">
+        <is>
+          <t>4,8 km</t>
+        </is>
+      </c>
+      <c r="U30" s="15" t="n"/>
+      <c r="V30" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/fc600e74-bcb0-42db-b805-606f29b362d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Nails Taxi Service</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Spessartstr. 8</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>0163 6 44 00 24</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="inlineStr">
+        <is>
+          <t>nailstaxi@web.de</t>
+        </is>
+      </c>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
+      <c r="P31" s="13" t="n"/>
+      <c r="Q31" s="13" t="n"/>
+      <c r="R31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t>7,8 km</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="n"/>
+      <c r="V31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/38d8739e-0245-4436-83ff-12ad0304b301</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>ECT ECO TAXI Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>Alte Schmelze 19</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>0611 1 66 78 46</t>
+        </is>
+      </c>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="15" t="n"/>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="14" t="n"/>
+      <c r="S32" s="14" t="n"/>
+      <c r="T32" s="15" t="inlineStr">
+        <is>
+          <t>4,8 km</t>
+        </is>
+      </c>
+      <c r="U32" s="15" t="n"/>
+      <c r="V32" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/84165ff2-0ef2-4fb6-abd6-c06930c86670</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>FTZ Funk-Taxi-Zentrale Wiesbaden GmbH</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Bote, Chauffeur, Dialysefahrten, Events, Fahrzeugüberführung, Flughafentransfer, Hochzeiten, Krankenfahrten, Kurierfahrten, Personenbeförderung, Personentransporte, Rechnungsfahrte</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Alte Schmelze 19</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>0611 9 99 99</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="inlineStr">
+        <is>
+          <t>info@taxi-wiesbaden.de</t>
+        </is>
+      </c>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>http://www.taxi-wiesbaden.de/</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="n"/>
+      <c r="Q33" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00; Fe 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R33" s="12" t="n"/>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="13" t="inlineStr">
+        <is>
+          <t>4,8 km</t>
+        </is>
+      </c>
+      <c r="U33" s="13" t="n"/>
+      <c r="V33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/71457645-cde9-4ee3-9034-d6bc5721cfaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Toma Michael</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Limousinenservice, Krankenfahrten, Taxifahrt</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Karl-Drebert-Str. 19</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="inlineStr">
+        <is>
+          <t>0611 8 90 20 88</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="15" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="14" t="n"/>
+      <c r="S34" s="14" t="n"/>
+      <c r="T34" s="15" t="inlineStr">
+        <is>
+          <t>4,9 km</t>
+        </is>
+      </c>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/71bbef9f-188c-413e-ac47-477be9517528</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Ahmed Mahmood Taxiunternehmer Taxi</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Taxen, Limousinenservice</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Lilienthalstr. 36</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="n"/>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>0173 6 98 54 53</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="13" t="n"/>
+      <c r="N35" s="13" t="n"/>
+      <c r="O35" s="13" t="n"/>
+      <c r="P35" s="13" t="n"/>
+      <c r="Q35" s="13" t="n"/>
+      <c r="R35" s="12" t="n"/>
+      <c r="S35" s="12" t="n"/>
+      <c r="T35" s="13" t="inlineStr">
+        <is>
+          <t>5,1 km</t>
+        </is>
+      </c>
+      <c r="U35" s="13" t="n"/>
+      <c r="V35" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5b284500-5796-4ab9-80ab-d014e4aaed79</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Griesenbrock Harald</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Taxi, Airportservice</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>65205</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Wandersmannstr. 9</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="inlineStr">
+        <is>
+          <t>0611 70 17 60</t>
+        </is>
+      </c>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="15" t="n"/>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="14" t="n"/>
+      <c r="S36" s="14" t="n"/>
+      <c r="T36" s="15" t="inlineStr">
+        <is>
+          <t>5,2 km</t>
+        </is>
+      </c>
+      <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/b3b86835-1f99-47d4-b67c-8e5ca63ac80e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Ruf</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Flughafenfahrten, Flughafenshuttle, Taxi, Großraumtaxi, Flughafentransfer, Krankenfahrten</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>65203</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>Hilgersstr. 3</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>06134 6 20 08</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="13" t="inlineStr">
+        <is>
+          <t>info@taxiruf-kastel.de</t>
+        </is>
+      </c>
+      <c r="N37" s="13" t="n"/>
+      <c r="O37" s="13" t="inlineStr">
+        <is>
+          <t>http://www.taxiruf-kastel.de/</t>
+        </is>
+      </c>
+      <c r="P37" s="13" t="n"/>
+      <c r="Q37" s="13" t="n"/>
+      <c r="R37" s="12" t="n"/>
+      <c r="S37" s="12" t="n"/>
+      <c r="T37" s="13" t="inlineStr">
+        <is>
+          <t>6 km</t>
+        </is>
+      </c>
+      <c r="U37" s="13" t="n"/>
+      <c r="V37" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/4103945c-e66e-4377-a6dd-569f9090298f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>TAXI HIDO Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Deutschland weit beförderung, flughafentransfer, Taxi</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>55120</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Am Hipperich 2c</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>0174 8 60 15 77</t>
+        </is>
+      </c>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="15" t="n"/>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>taximainz@gmx.de</t>
+        </is>
+      </c>
+      <c r="N38" s="15" t="n"/>
+      <c r="O38" s="15" t="inlineStr">
+        <is>
+          <t>http://www.taxi.de/unternehmen/taxi-hido-55120/</t>
+        </is>
+      </c>
+      <c r="P38" s="15" t="n"/>
+      <c r="Q38" s="15" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R38" s="14" t="n"/>
+      <c r="S38" s="14" t="n"/>
+      <c r="T38" s="15" t="inlineStr">
+        <is>
+          <t>7,4 km</t>
+        </is>
+      </c>
+      <c r="U38" s="15" t="n"/>
+      <c r="V38" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/867e09cc-2662-486a-81fe-b05802fde4b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>City Taxi Mainz</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="inlineStr">
+        <is>
+          <t>55118</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>Moselstr. 31</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>06131 4 93 03 77</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="13" t="inlineStr">
+        <is>
+          <t>taxi7mainz@gmail.com</t>
+        </is>
+      </c>
+      <c r="N39" s="13" t="n"/>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>http://taximainz.info/</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="n"/>
+      <c r="Q39" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R39" s="12" t="n"/>
+      <c r="S39" s="12" t="n"/>
+      <c r="T39" s="13" t="inlineStr">
+        <is>
+          <t>7,8 km</t>
+        </is>
+      </c>
+      <c r="U39" s="13" t="n"/>
+      <c r="V39" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/bbcaf94c-fa8d-44b8-a47c-fd003a69e6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Taxi Munish Taxiunternehmen, Büro Mainz-Kostheim</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Flughafentransfer, Personenbeförderungen, Taxifahrten, Transferservice, Schülerbeförderung</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>55246</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr">
+        <is>
+          <t>Mainz-Kostheim</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Schiersteiner Str. 9</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="15" t="inlineStr">
+        <is>
+          <t>06134 95 69 50</t>
+        </is>
+      </c>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="15" t="n"/>
+      <c r="M40" s="15" t="inlineStr">
+        <is>
+          <t>info@taxi-munish.de</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="n"/>
+      <c r="O40" s="15" t="inlineStr">
+        <is>
+          <t>http://www.taxi-munish.de/</t>
+        </is>
+      </c>
+      <c r="P40" s="15" t="n"/>
+      <c r="Q40" s="15" t="n"/>
+      <c r="R40" s="14" t="n"/>
+      <c r="S40" s="14" t="n"/>
+      <c r="T40" s="15" t="inlineStr">
+        <is>
+          <t>9,5 km</t>
+        </is>
+      </c>
+      <c r="U40" s="15" t="n"/>
+      <c r="V40" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/fc696707-d73e-466f-8d05-77f2dacb26f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Stephan</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Rechnungsfahrten, Gruppenfahrten, Krankentransporte</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>55246</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>Mainz-Kostheim</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>Schiersteiner Str. 9</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>06134 28 08 86</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>info@taxi-stephan.de</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="n"/>
+      <c r="O41" s="13" t="inlineStr">
+        <is>
+          <t>http://www.taxi-stephan.de/</t>
+        </is>
+      </c>
+      <c r="P41" s="13" t="n"/>
+      <c r="Q41" s="13" t="n"/>
+      <c r="R41" s="12" t="n"/>
+      <c r="S41" s="12" t="n"/>
+      <c r="T41" s="13" t="inlineStr">
+        <is>
+          <t>9,5 km</t>
+        </is>
+      </c>
+      <c r="U41" s="13" t="n"/>
+      <c r="V41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ee99c8b1-43cc-4b8d-b045-ce419a981497</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Dawood Taxi - Mohammad Dawood Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Arztfahrten, Taxifahrt</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>65185</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="15" t="inlineStr">
+        <is>
+          <t>0176 22 88 26 71</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="n"/>
+      <c r="L42" s="15" t="n"/>
+      <c r="M42" s="15" t="n"/>
+      <c r="N42" s="15" t="n"/>
+      <c r="O42" s="15" t="n"/>
+      <c r="P42" s="15" t="n"/>
+      <c r="Q42" s="15" t="n"/>
+      <c r="R42" s="14" t="n"/>
+      <c r="S42" s="14" t="n"/>
+      <c r="T42" s="15" t="n"/>
+      <c r="U42" s="15" t="n"/>
+      <c r="V42" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/a6615796-6259-4122-a2ef-7bc923126452</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>Taxi Mietwagen. S. Hussain</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>Taxen, Krankentransport, Mietwagen</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F43" s="13" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Carl-von-Ossietzky-Str. 19</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="n"/>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>0176 31 64 19 91</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="13" t="inlineStr">
+        <is>
+          <t>taximietwagen.wiesbaden@gmail.com</t>
+        </is>
+      </c>
+      <c r="N43" s="13" t="n"/>
+      <c r="O43" s="13" t="n"/>
+      <c r="P43" s="13" t="n"/>
+      <c r="Q43" s="13" t="inlineStr">
+        <is>
+          <t>Mo 00:00-24:00; Di 00:00-24:00; Mi 00:00-24:00; Do 00:00-24:00; Fr 00:00-24:00; Sa 00:00-24:00; So 00:00-24:00</t>
+        </is>
+      </c>
+      <c r="R43" s="12" t="n"/>
+      <c r="S43" s="12" t="n"/>
+      <c r="T43" s="13" t="inlineStr">
+        <is>
+          <t>2,9 km</t>
+        </is>
+      </c>
+      <c r="U43" s="13" t="n"/>
+      <c r="V43" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/22123260-7abe-4331-9649-45d194f489da</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>FTD Funk-Taxi-Dienst eG</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Airportservice, Airportshuttle, Airporttaxi, Airporttransfer, Airporttrasfer, Botenfahrt, Botenfahrten, Botenservice, CAB, Flughafen-Transfer, Flughafentransfer, Flughafenzubringer</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Steinmetzstr. 2</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="15" t="inlineStr">
+        <is>
+          <t>0611 44 44 44</t>
+        </is>
+      </c>
+      <c r="K44" s="15" t="n"/>
+      <c r="L44" s="15" t="n"/>
+      <c r="M44" s="15" t="inlineStr">
+        <is>
+          <t>info@taxi-444444.de</t>
+        </is>
+      </c>
+      <c r="N44" s="15" t="n"/>
+      <c r="O44" s="15" t="inlineStr">
+        <is>
+          <t>https://www.taxi-444444.de/</t>
+        </is>
+      </c>
+      <c r="P44" s="15" t="n"/>
+      <c r="Q44" s="15" t="inlineStr">
+        <is>
+          <t>Mo 10:00-17:00; Di 10:00-17:00; Mi 10:00-17:00; Do 10:00-17:00; Fr 10:00-17:00</t>
+        </is>
+      </c>
+      <c r="R44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S44" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T44" s="15" t="inlineStr">
+        <is>
+          <t>1,7 km</t>
+        </is>
+      </c>
+      <c r="U44" s="15" t="n"/>
+      <c r="V44" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/7b28267e-652c-4191-abc0-5da3fcec3f48</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Auto König Wiesbaden</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Autoreparaturen, Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>65197</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>Annastr. 11</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="n"/>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>0611 42 22 22</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="13" t="inlineStr">
+        <is>
+          <t>info@autokonig.de</t>
+        </is>
+      </c>
+      <c r="N45" s="13" t="n"/>
+      <c r="O45" s="13" t="inlineStr">
+        <is>
+          <t>http://www.xn--auto-knig-wiesbaden-v6b.de/</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="n"/>
+      <c r="Q45" s="13" t="inlineStr">
+        <is>
+          <t>Mo 08:00-17:00; Di 08:00-17:00; Mi 08:00-17:00; Do 08:00-17:00; Fr 08:00-14:00</t>
+        </is>
+      </c>
+      <c r="R45" s="12" t="n"/>
+      <c r="S45" s="12" t="n"/>
+      <c r="T45" s="13" t="inlineStr">
+        <is>
+          <t>3 km</t>
+        </is>
+      </c>
+      <c r="U45" s="13" t="n"/>
+      <c r="V45" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/06864375-783f-4627-b801-23bb6bc32ba1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Transfer Deluxe Limousinenservice</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Business, Chauffeurservice, Fahrservice, Flughafentransfer, Junggesellenabschiede, Limousinenservice, Promotion, Roadshows, Schulabschlüsse, Shoppingtour, Shuttles, Stadtrundfahrte</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>65203</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbadener Landstr. 18</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="15" t="inlineStr">
+        <is>
+          <t>0611 1 83 33 33</t>
+        </is>
+      </c>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="inlineStr">
+        <is>
+          <t>info@transferdeluxe.eu</t>
+        </is>
+      </c>
+      <c r="N46" s="15" t="n"/>
+      <c r="O46" s="15" t="inlineStr">
+        <is>
+          <t>http://www.transferdeluxe.eu/</t>
+        </is>
+      </c>
+      <c r="P46" s="15" t="n"/>
+      <c r="Q46" s="15" t="n"/>
+      <c r="R46" s="14" t="n"/>
+      <c r="S46" s="14" t="n"/>
+      <c r="T46" s="15" t="inlineStr">
+        <is>
+          <t>6,3 km</t>
+        </is>
+      </c>
+      <c r="U46" s="15" t="n"/>
+      <c r="V46" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/6162c5cf-858d-454a-a90e-cbe03b2c46ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>Mainspitz Krankentransport</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Taxi</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>55246</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Mainz-Kostheim</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Kostheimer Landstr. 89a</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>0800 7 27 28 80</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="n"/>
+      <c r="O47" s="13" t="n"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="n"/>
+      <c r="R47" s="12" t="n"/>
+      <c r="S47" s="12" t="n"/>
+      <c r="T47" s="13" t="inlineStr">
+        <is>
+          <t>9,3 km</t>
+        </is>
+      </c>
+      <c r="U47" s="13" t="n"/>
+      <c r="V47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/81c07584-3fb8-4009-b30b-7a3580f4d008</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Aban International Reisen GmbH</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Taxiunternehmen</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Afrika Spezialist, Billigflüge, Flugbörse, Reisen nach Iran, Flugtickets weltweit, Günstige Flüge, Iran Air, Lastminute, Visum für Iran, Airport-Taxi</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>60329</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>Am Hauptbahnhof 18</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="n"/>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>069 23 37 45</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="n"/>
+      <c r="L48" s="15" t="n"/>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>info@abanreisen.de</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="n"/>
+      <c r="O48" s="15" t="inlineStr">
+        <is>
+          <t>http://www.abanreisen.de/</t>
+        </is>
+      </c>
+      <c r="P48" s="15" t="n"/>
+      <c r="Q48" s="15" t="inlineStr">
+        <is>
+          <t>Mo 09:00-18:00; Di 09:00-18:00; Mi 09:00-18:00; Do 09:00-18:00; Fr 09:00-18:00; Sa 10:00-13:00</t>
+        </is>
+      </c>
+      <c r="R48" s="14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S48" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="15" t="inlineStr">
+        <is>
+          <t>30,1 km</t>
+        </is>
+      </c>
+      <c r="U48" s="15" t="n"/>
+      <c r="V48" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/f0c65462-3748-48d8-85be-8635269ca1fd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/P(Path)/RP(Rhine-Path)/RheinWegDE/Wiesbaden.xlsx
+++ b/P(Path)/RP(Rhine-Path)/RheinWegDE/Wiesbaden.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="restaurant" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kino" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="taxi" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ferienwohnung" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -46621,4 +46622,1570 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="7" min="1" max="1"/>
+    <col width="34.66" customWidth="1" style="7" min="2" max="2"/>
+    <col width="22" customWidth="1" style="7" min="3" max="3"/>
+    <col width="36" customWidth="1" style="7" min="4" max="4"/>
+    <col width="12" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10" customWidth="1" style="7" min="6" max="6"/>
+    <col width="28" customWidth="1" style="7" min="7" max="7"/>
+    <col width="28" customWidth="1" style="7" min="8" max="8"/>
+    <col width="18" customWidth="1" style="7" min="9" max="9"/>
+    <col width="16" customWidth="1" style="7" min="10" max="10"/>
+    <col width="16" customWidth="1" style="7" min="11" max="11"/>
+    <col width="16" customWidth="1" style="7" min="12" max="12"/>
+    <col width="32" customWidth="1" style="7" min="13" max="13"/>
+    <col width="32" customWidth="1" style="7" min="14" max="14"/>
+    <col width="40" customWidth="1" style="7" min="15" max="15"/>
+    <col width="42" customWidth="1" style="7" min="16" max="16"/>
+    <col width="26" customWidth="1" style="7" min="17" max="17"/>
+    <col width="9" customWidth="1" style="7" min="18" max="18"/>
+    <col width="10" customWidth="1" style="7" min="19" max="19"/>
+    <col width="11" customWidth="1" style="7" min="20" max="20"/>
+    <col width="16" customWidth="1" style="7" min="21" max="21"/>
+    <col width="45" customWidth="1" style="7" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" s="7">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>🏠  Ferienwohnung – Wiesbaden  ·  19 Companies  ·  Source: GelbeSeiten</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="7">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Business Description</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>ZIP Code</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>Street</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>Contact Person</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 1</t>
+        </is>
+      </c>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 2</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>Telephone 3</t>
+        </is>
+      </c>
+      <c r="M2" s="11" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N2" s="11" t="inlineStr">
+        <is>
+          <t>Email 2</t>
+        </is>
+      </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="P2" s="11" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+      <c r="Q2" s="11" t="inlineStr">
+        <is>
+          <t>Opening Hours</t>
+        </is>
+      </c>
+      <c r="R2" s="11" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="inlineStr">
+        <is>
+          <t># Reviews</t>
+        </is>
+      </c>
+      <c r="T2" s="11" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="U2" s="11" t="inlineStr">
+        <is>
+          <t>Badge / Partner</t>
+        </is>
+      </c>
+      <c r="V2" s="11" t="inlineStr">
+        <is>
+          <t>GelbeSeiten URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>DERTOUR Reisebüro</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Fernreisen, Kreuzfahrten, Rundreisen, Ferienwohnung, Mietwagen, Flüge, Servicepaket, Reiseschutz</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>65183</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Mauritiusplatz 1</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>0611 34 61 10</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>wiesbaden4@dertour-reisebuero.de</t>
+        </is>
+      </c>
+      <c r="N3" s="13" t="n"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>http://www.dertour-reisebuero.de/wiesbaden4</t>
+        </is>
+      </c>
+      <c r="P3" s="13" t="n"/>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>Mo 10:00-18:00; Di 10:00-18:00; Mi 10:00-18:00; Do 10:00-18:00; Fr 10:00-18:00; Sa 10:00-14:00</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="n"/>
+      <c r="S3" s="12" t="n"/>
+      <c r="T3" s="13" t="inlineStr">
+        <is>
+          <t>463 m</t>
+        </is>
+      </c>
+      <c r="U3" s="13" t="n"/>
+      <c r="V3" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/8979c275-4c71-4305-864b-ba2f7da7de5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>DERTOUR Reisebüro</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Fernreisen, Kreuzfahrten, Rundreisen, Ferienwohnung, Mietwagen, Flüge, Servicepaket, Reiseschutz</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>65185</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Friedrichstraße 34</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>0611 30 20 97</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>wiesbaden2@dertour-reisebuero.de</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n"/>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>http://www.dertour-reisebuero.de/wiesbaden2</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="n"/>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>Mo 10:00-18:00; Di 10:00-18:00; Mi 10:00-18:00; Do 10:00-18:00; Fr 10:00-18:00</t>
+        </is>
+      </c>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="15" t="inlineStr">
+        <is>
+          <t>604 m</t>
+        </is>
+      </c>
+      <c r="U4" s="15" t="n"/>
+      <c r="V4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/d6e13499-f7d7-4201-bf30-6fed1a4817b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Schramm Bernhard u. Maria-Luise Ferienwohnungvermietung</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungvermietung</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>65189</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Mainzer Str. 88B</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>0611 76 10 68</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>webmaster@wiesbaden-ferienwohnungen.de</t>
+        </is>
+      </c>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.wiesbaden-ferienwohnungen.de/</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="12" t="n"/>
+      <c r="S5" s="12" t="n"/>
+      <c r="T5" s="13" t="inlineStr">
+        <is>
+          <t>1,8 km</t>
+        </is>
+      </c>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/6c77c1c6-fb1e-4ced-82f7-f928d06e0c47</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Doleschal Ferienwohnung</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Appartment, Ferienwohnung, Zeitmiete</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>65187</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Volkerstr. 47</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>0611 2 38 89 79</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>info@ferienwohnung-doleschal.de</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>http://www.ferienwohnung-doleschal.de/</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>2,9 km</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/8c231103-c7b6-4b04-b652-32557b5c659e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Wohnraum Becker Ferienwohnungen in Wiesbaden</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen, Appartmentvermietung</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>65199</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Helgoländer Str. 8</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>0611 4 19 01 05</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>info@wohnraumbecker.de</t>
+        </is>
+      </c>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>http://www.wohnraumbecker.de/</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="13" t="n"/>
+      <c r="R7" s="12" t="n"/>
+      <c r="S7" s="12" t="n"/>
+      <c r="T7" s="13" t="inlineStr">
+        <is>
+          <t>3,6 km</t>
+        </is>
+      </c>
+      <c r="U7" s="13" t="n"/>
+      <c r="V7" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/064d40d2-8785-41d9-8794-ab619d8cf034</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Apartment Aaron-Ferienwohnung</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>65203</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Wingertstr. 24c</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>0611 24 08 14 34</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>ferienwohnung.aaron@gmail.com</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>http://www.ferienwohnung-aaron-wiesbaden.de/</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="14" t="n"/>
+      <c r="S8" s="14" t="n"/>
+      <c r="T8" s="15" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/02bd43c9-b59d-4d85-8f5d-7cc0627a7c13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Schmuckkästle</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>Küferstr. 12</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>0176 56 84 48 12</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="12" t="n"/>
+      <c r="S9" s="12" t="n"/>
+      <c r="T9" s="13" t="inlineStr">
+        <is>
+          <t>5,8 km</t>
+        </is>
+      </c>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5127315f-8b04-4d89-ade7-40733484705e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Schmuckkästle Vermietung von Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Ferienappartment, Weinhandlung, Riesling</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Küferstr. 12</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>0611 58 01 88 10</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>info@kunsttrifftwein.de</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.schmuckkaestle-schierstein.de/</t>
+        </is>
+      </c>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="inlineStr">
+        <is>
+          <t>Do 16:00-18:30; Fr 16:00-18:30</t>
+        </is>
+      </c>
+      <c r="R10" s="14" t="n"/>
+      <c r="S10" s="14" t="n"/>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>5,8 km</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/9cedab98-76a4-48ef-b76a-de2331cf3a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Maurer Anja Vermietung von Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Apartmentvermietung</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>65207</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Bernsteinstr. 4A</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>06127 9 86 80 56</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>apartments-maurer@gmx.de</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>http://www.apartments-maurer.de/</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="n"/>
+      <c r="R11" s="12" t="n"/>
+      <c r="S11" s="12" t="n"/>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>6,7 km</t>
+        </is>
+      </c>
+      <c r="U11" s="13" t="n"/>
+      <c r="V11" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/b3836c61-ee83-4750-8160-da33fb64b145</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Pietscher Ferienhaus</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Ferienhaus</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>55120</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Hauptstr. 116</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>0151 16 70 50 60</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>ferienhaus@pietscher.de</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="inlineStr">
+        <is>
+          <t>http://www.pietscher.de/</t>
+        </is>
+      </c>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="14" t="n"/>
+      <c r="S12" s="14" t="n"/>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>7 km</t>
+        </is>
+      </c>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/2bc78ccd-7566-4491-afdc-66b96d300786</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Herberge Hof Armada</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Fremdenzimmer, Pferdepension, Lernbauernhof</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>Hof Armada 1</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>0611 72 38 77 50</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>n.schuster@hof-armada.com</t>
+        </is>
+      </c>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>http://www.hof-armada.com/</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t>7,1 km</t>
+        </is>
+      </c>
+      <c r="U13" s="13" t="n"/>
+      <c r="V13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/38b2edb5-92c4-4ea2-8743-31ef1154021f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Aparthotel Parkallee Appartements</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Appartements, Suiten</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>55257</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Budenheim</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Budenheimer Parkallee 9</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>06139 29 30 28</t>
+        </is>
+      </c>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>info@aparthotel-mainz.de</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="inlineStr">
+        <is>
+          <t>http://aparthotel-mainz.de/</t>
+        </is>
+      </c>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>7,5 km</t>
+        </is>
+      </c>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/ec719e4b-84bd-47c8-a7dd-d3f579f181ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Maurer Apartments Maurer</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Appartements, Übernachtungen</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>65207</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>06127 9 86 80 56</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>info@apartments-freizeitpark.de</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.apartments-freizeitpark.de/</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="13" t="n"/>
+      <c r="R15" s="12" t="n"/>
+      <c r="S15" s="12" t="n"/>
+      <c r="T15" s="13" t="n"/>
+      <c r="U15" s="13" t="n"/>
+      <c r="V15" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/52b0bfcf-05cc-437c-870b-97a20015c9be</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>FeWo Gästehäuser Irmgard u. Willi Becker Gästehaus</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Leierweg 1</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>0611 9 42 77-0</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
+      <c r="T16" s="15" t="inlineStr">
+        <is>
+          <t>5,9 km</t>
+        </is>
+      </c>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/f332adf6-a44d-4b47-921f-3433d908c48b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Gästehaus Stapf</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Gästehaus, Messehotel, Hotel, Ferienwohnung, Gästezimmer, Übernachtungen, Pension, Boardinghouse, Monteurzimmer</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>65187</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>Lützowstr. 4</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>0611 8 62 02</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>info@gaestehaus-stapf.de</t>
+        </is>
+      </c>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gaestehaus-stapf.de/</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
+      <c r="R17" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S17" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>3,7 km</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="n"/>
+      <c r="V17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5295e7c0-4b4e-4c93-8c2b-a98b8dfb6277</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Seifert Rainer TV - An- und Verkauf</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnung Wiesbaden, Unterkunft, Zimmervermietung</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>65189</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Zweibörnstr. 13</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>0611 4 77 05</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t>rainerseifert13@googlemail.com</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ferienwohnung-wiesbaden-zweibornstrasse.de/</t>
+        </is>
+      </c>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>2,7 km</t>
+        </is>
+      </c>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/0564ea8c-7dee-4223-ac92-e7efd8bed1d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Günaydin Masholtan Hotel</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Gästehaus, Dreibettzimmer, Vierbettzimmer, Übernachtung, Hotel, günstiges Hotel, Ferienwohnung, Monteurzimmer, Messezimmer, Monteurunterkunft, günstige Übernachtung, Hotel garni, M</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>65201</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Wiesbaden</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Karl-Lehr-Str. 24</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>0611 2 00 20</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>hotel.link@t-online.de</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.hotellink-wiesbaden.de/</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="inlineStr">
+        <is>
+          <t>Mo 07:00-22:00; Di 07:00-22:00; Mi 07:00-22:00; Do 07:00-22:00; Fr 07:00-22:00; Sa 07:00-22:00; So 07:00-22:00</t>
+        </is>
+      </c>
+      <c r="R19" s="12" t="n"/>
+      <c r="S19" s="12" t="n"/>
+      <c r="T19" s="13" t="inlineStr">
+        <is>
+          <t>5,4 km</t>
+        </is>
+      </c>
+      <c r="U19" s="13" t="n"/>
+      <c r="V19" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/4828f0e0-afd1-483a-8d3f-56e4e1c83ebf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Reisestern Reisebüro</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Omnibus, Omnibusbetriebe, Kreuzfahrt, Reisebüro, Ferienhaus, Ferienwohnung, Fernreise, Camperreise, Last Minute Reise, Städtereise, Busreise, Strandurlaub, Schiffsreise, Wanderreis</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>65396</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Walluf</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Erikaweg 2</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>06123 70 44 00</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>info@reisestern-walluf.de</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="inlineStr">
+        <is>
+          <t>http://www.reisebuero-reisestern.de/</t>
+        </is>
+      </c>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="inlineStr">
+        <is>
+          <t>Mo 09:30-13:00; Mo 15:00-18:30; Di 09:30-13:00; Di 15:00-18:30; Mi 09:30-13:00; Do 09:30-13:00; Do 15:00-18:30; Fr 09:30-13:00; Fr 15:00-18:30; Sa 10:00-13:00</t>
+        </is>
+      </c>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
+      <c r="T20" s="15" t="inlineStr">
+        <is>
+          <t>7,9 km</t>
+        </is>
+      </c>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/5d4fd17d-24cd-4ed1-9055-51a95fcf1904</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Apartmenthaus am Achteck</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Ferienwohnungen</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>37,7 km</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Hessen</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>64289</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>Mauerstr. 15</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>0179 1 22 10 30</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>rene.bach@web.de</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>https://apartmenthaus-am-achteck.bookingturbo.com/de/</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="inlineStr">
+        <is>
+          <t>Apartments, Apartmentvermietung, Ferienwohnung, Kurzzeitwohnung, Messeunterkunft, Messezimmer, Monteurswohnung, Monteurunterkunft, Zimmervermietung, Messeapartments</t>
+        </is>
+      </c>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="12" t="n"/>
+      <c r="T21" s="13" t="n"/>
+      <c r="U21" s="13" t="n"/>
+      <c r="V21" s="13" t="inlineStr">
+        <is>
+          <t>https://www.gelbeseiten.de/gsbiz/68a73bb6-672f-48e3-b677-2e341473fd67</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>